--- a/education_forms/043_education_platform_interview_question_form--education_forms.xlsx
+++ b/education_forms/043_education_platform_interview_question_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>option 6</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>option 6</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>option 6</t>
         </is>
       </c>
     </row>
